--- a/docs/开发工作量评估表.xlsx
+++ b/docs/开发工作量评估表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowWidth="22192" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="开发工作量评估表" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="181">
   <si>
     <t>南丰蜜桔模型管理系统-开发工作量评估表</t>
   </si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>病虫害预测报告，含报告生成、预览与历史记录</t>
-  </si>
-  <si>
-    <t>病虫害模型数据校准，含预测结果对比与参数调整</t>
   </si>
   <si>
     <t>防控方案</t>
@@ -590,7 +587,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -626,12 +623,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -1218,133 +1209,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1377,7 +1368,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -1389,7 +1380,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1739,7 +1730,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="11.5309734513274" customWidth="1"/>
@@ -2018,40 +2009,40 @@
     </row>
     <row r="21" ht="27.75" customHeight="1" spans="1:6">
       <c r="A21" s="4"/>
-      <c r="B21" s="8"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="6" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="7"/>
+        <v>46</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="F21" s="7"/>
     </row>
     <row r="22" ht="27.75" customHeight="1" spans="1:6">
       <c r="A22" s="4"/>
-      <c r="B22" s="9"/>
+      <c r="B22" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="C22" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>24</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
     <row r="23" ht="27.75" customHeight="1" spans="1:6">
       <c r="A23" s="4"/>
-      <c r="B23" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="B23" s="8"/>
       <c r="C23" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -2060,10 +2051,10 @@
       <c r="A24" s="4"/>
       <c r="B24" s="8"/>
       <c r="C24" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -2072,10 +2063,10 @@
       <c r="A25" s="4"/>
       <c r="B25" s="8"/>
       <c r="C25" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
@@ -2084,10 +2075,10 @@
       <c r="A26" s="4"/>
       <c r="B26" s="8"/>
       <c r="C26" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -2096,10 +2087,10 @@
       <c r="A27" s="4"/>
       <c r="B27" s="8"/>
       <c r="C27" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -2108,10 +2099,10 @@
       <c r="A28" s="4"/>
       <c r="B28" s="8"/>
       <c r="C28" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -2120,10 +2111,10 @@
       <c r="A29" s="4"/>
       <c r="B29" s="8"/>
       <c r="C29" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -2132,10 +2123,10 @@
       <c r="A30" s="4"/>
       <c r="B30" s="8"/>
       <c r="C30" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -2144,100 +2135,100 @@
       <c r="A31" s="4"/>
       <c r="B31" s="8"/>
       <c r="C31" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="1:6">
       <c r="A32" s="4"/>
-      <c r="B32" s="8"/>
+      <c r="B32" s="9"/>
       <c r="C32" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
     <row r="33" ht="27.75" customHeight="1" spans="1:6">
       <c r="A33" s="4"/>
-      <c r="B33" s="9"/>
+      <c r="B33" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="C33" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="7"/>
+        <v>71</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="F33" s="7"/>
     </row>
     <row r="34" ht="27.75" customHeight="1" spans="1:6">
       <c r="A34" s="4"/>
-      <c r="B34" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="B34" s="8"/>
       <c r="C34" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>24</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
     <row r="35" ht="27.75" customHeight="1" spans="1:6">
       <c r="A35" s="4"/>
       <c r="B35" s="8"/>
       <c r="C35" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" spans="1:6">
       <c r="A36" s="4"/>
-      <c r="B36" s="8"/>
+      <c r="B36" s="9"/>
       <c r="C36" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" spans="1:6">
       <c r="A37" s="4"/>
-      <c r="B37" s="9"/>
+      <c r="B37" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="C37" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" spans="1:6">
       <c r="A38" s="4"/>
-      <c r="B38" s="5" t="s">
-        <v>79</v>
-      </c>
+      <c r="B38" s="8"/>
       <c r="C38" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
@@ -2246,10 +2237,10 @@
       <c r="A39" s="4"/>
       <c r="B39" s="8"/>
       <c r="C39" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
@@ -2258,86 +2249,86 @@
       <c r="A40" s="4"/>
       <c r="B40" s="8"/>
       <c r="C40" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
     </row>
     <row r="41" ht="27.75" customHeight="1" spans="1:6">
       <c r="A41" s="4"/>
-      <c r="B41" s="8"/>
+      <c r="B41" s="9"/>
       <c r="C41" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
     </row>
     <row r="42" ht="27.75" customHeight="1" spans="1:6">
       <c r="A42" s="4"/>
-      <c r="B42" s="9"/>
+      <c r="B42" s="5" t="s">
+        <v>89</v>
+      </c>
       <c r="C42" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
     </row>
     <row r="43" ht="27.75" customHeight="1" spans="1:6">
       <c r="A43" s="4"/>
-      <c r="B43" s="5" t="s">
-        <v>90</v>
-      </c>
+      <c r="B43" s="9"/>
       <c r="C43" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
     </row>
     <row r="44" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A44" s="4"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" s="6" t="s">
+      <c r="A44" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
     </row>
     <row r="45" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
+      <c r="B45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
     </row>
     <row r="46" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A46" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>97</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -2346,10 +2337,10 @@
       <c r="A47" s="4"/>
       <c r="B47" s="8"/>
       <c r="C47" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
@@ -2358,10 +2349,10 @@
       <c r="A48" s="4"/>
       <c r="B48" s="8"/>
       <c r="C48" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
@@ -2370,10 +2361,10 @@
       <c r="A49" s="4"/>
       <c r="B49" s="8"/>
       <c r="C49" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
@@ -2382,10 +2373,10 @@
       <c r="A50" s="4"/>
       <c r="B50" s="8"/>
       <c r="C50" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
@@ -2394,48 +2385,48 @@
       <c r="A51" s="4"/>
       <c r="B51" s="8"/>
       <c r="C51" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
     </row>
     <row r="52" ht="27.75" customHeight="1" spans="1:6">
       <c r="A52" s="4"/>
-      <c r="B52" s="8"/>
+      <c r="B52" s="9"/>
       <c r="C52" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
     </row>
     <row r="53" ht="27.75" customHeight="1" spans="1:6">
       <c r="A53" s="4"/>
-      <c r="B53" s="9"/>
+      <c r="B53" s="5" t="s">
+        <v>113</v>
+      </c>
       <c r="C53" s="6" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
     </row>
     <row r="54" ht="27.75" customHeight="1" spans="1:6">
       <c r="A54" s="4"/>
-      <c r="B54" s="5" t="s">
-        <v>114</v>
-      </c>
+      <c r="B54" s="8"/>
       <c r="C54" s="6" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
@@ -2444,10 +2435,10 @@
       <c r="A55" s="4"/>
       <c r="B55" s="8"/>
       <c r="C55" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
@@ -2456,10 +2447,10 @@
       <c r="A56" s="4"/>
       <c r="B56" s="8"/>
       <c r="C56" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
@@ -2468,10 +2459,10 @@
       <c r="A57" s="4"/>
       <c r="B57" s="8"/>
       <c r="C57" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E57" s="7"/>
       <c r="F57" s="7"/>
@@ -2480,10 +2471,10 @@
       <c r="A58" s="4"/>
       <c r="B58" s="8"/>
       <c r="C58" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
@@ -2492,10 +2483,10 @@
       <c r="A59" s="4"/>
       <c r="B59" s="8"/>
       <c r="C59" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
@@ -2504,10 +2495,10 @@
       <c r="A60" s="4"/>
       <c r="B60" s="8"/>
       <c r="C60" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -2516,102 +2507,104 @@
       <c r="A61" s="4"/>
       <c r="B61" s="8"/>
       <c r="C61" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E61" s="7"/>
       <c r="F61" s="7"/>
     </row>
     <row r="62" ht="27.75" customHeight="1" spans="1:6">
       <c r="A62" s="4"/>
-      <c r="B62" s="8"/>
+      <c r="B62" s="9"/>
       <c r="C62" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
     </row>
     <row r="63" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A63" s="4"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D63" s="6" t="s">
+      <c r="A63" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
     </row>
     <row r="64" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
+      <c r="B64" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
     </row>
     <row r="65" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A65" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>136</v>
+      <c r="A65" s="4"/>
+      <c r="B65" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E65" s="7"/>
+        <v>139</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="F65" s="7"/>
     </row>
     <row r="66" ht="27.75" customHeight="1" spans="1:6">
       <c r="A66" s="4"/>
-      <c r="B66" s="5" t="s">
-        <v>138</v>
-      </c>
+      <c r="B66" s="9"/>
       <c r="C66" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>24</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="E66" s="7"/>
       <c r="F66" s="7"/>
     </row>
     <row r="67" ht="27.75" customHeight="1" spans="1:6">
       <c r="A67" s="4"/>
-      <c r="B67" s="9"/>
+      <c r="B67" s="5" t="s">
+        <v>142</v>
+      </c>
       <c r="C67" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E67" s="7"/>
+        <v>144</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="F67" s="7"/>
     </row>
     <row r="68" ht="27.75" customHeight="1" spans="1:6">
       <c r="A68" s="4"/>
-      <c r="B68" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="B68" s="9"/>
       <c r="C68" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>24</v>
@@ -2620,66 +2613,64 @@
     </row>
     <row r="69" ht="27.75" customHeight="1" spans="1:6">
       <c r="A69" s="4"/>
-      <c r="B69" s="9"/>
+      <c r="B69" s="5" t="s">
+        <v>147</v>
+      </c>
       <c r="C69" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>24</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="E69" s="7"/>
       <c r="F69" s="7"/>
     </row>
     <row r="70" ht="27.75" customHeight="1" spans="1:6">
       <c r="A70" s="4"/>
-      <c r="B70" s="5" t="s">
-        <v>148</v>
-      </c>
+      <c r="B70" s="8"/>
       <c r="C70" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
     </row>
     <row r="71" ht="27.75" customHeight="1" spans="1:6">
       <c r="A71" s="4"/>
-      <c r="B71" s="8"/>
+      <c r="B71" s="9"/>
       <c r="C71" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E71" s="7"/>
       <c r="F71" s="7"/>
     </row>
     <row r="72" ht="27.75" customHeight="1" spans="1:6">
       <c r="A72" s="4"/>
-      <c r="B72" s="9"/>
+      <c r="B72" s="5" t="s">
+        <v>154</v>
+      </c>
       <c r="C72" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E72" s="7"/>
       <c r="F72" s="7"/>
     </row>
     <row r="73" ht="27.75" customHeight="1" spans="1:6">
       <c r="A73" s="4"/>
-      <c r="B73" s="5" t="s">
-        <v>155</v>
-      </c>
+      <c r="B73" s="8"/>
       <c r="C73" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
@@ -2688,34 +2679,36 @@
       <c r="A74" s="4"/>
       <c r="B74" s="8"/>
       <c r="C74" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
     </row>
     <row r="75" ht="27.75" customHeight="1" spans="1:6">
       <c r="A75" s="4"/>
-      <c r="B75" s="8"/>
+      <c r="B75" s="9"/>
       <c r="C75" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E75" s="7"/>
       <c r="F75" s="7"/>
     </row>
     <row r="76" ht="27.75" customHeight="1" spans="1:6">
       <c r="A76" s="4"/>
-      <c r="B76" s="9"/>
+      <c r="B76" s="7" t="s">
+        <v>162</v>
+      </c>
       <c r="C76" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
@@ -2723,41 +2716,39 @@
     <row r="77" ht="27.75" customHeight="1" spans="1:6">
       <c r="A77" s="4"/>
       <c r="B77" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
     </row>
     <row r="78" ht="27.75" customHeight="1" spans="1:6">
       <c r="A78" s="4"/>
-      <c r="B78" s="7" t="s">
-        <v>166</v>
+      <c r="B78" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
     </row>
     <row r="79" ht="27.75" customHeight="1" spans="1:6">
       <c r="A79" s="4"/>
-      <c r="B79" s="5" t="s">
-        <v>169</v>
-      </c>
+      <c r="B79" s="8"/>
       <c r="C79" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E79" s="7"/>
       <c r="F79" s="7"/>
@@ -2766,10 +2757,10 @@
       <c r="A80" s="4"/>
       <c r="B80" s="8"/>
       <c r="C80" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
@@ -2778,84 +2769,72 @@
       <c r="A81" s="4"/>
       <c r="B81" s="8"/>
       <c r="C81" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E81" s="7"/>
       <c r="F81" s="7"/>
     </row>
     <row r="82" ht="27.75" customHeight="1" spans="1:6">
       <c r="A82" s="4"/>
-      <c r="B82" s="8"/>
+      <c r="B82" s="9"/>
       <c r="C82" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E82" s="7"/>
       <c r="F82" s="7"/>
     </row>
     <row r="83" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A83" s="4"/>
-      <c r="B83" s="9"/>
-      <c r="C83" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D83" s="6" t="s">
+      <c r="A83" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="E83" s="7"/>
-      <c r="F83" s="7"/>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15"/>
+      <c r="D83" s="15"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
     </row>
     <row r="84" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="10"/>
-      <c r="F84" s="10"/>
-    </row>
-    <row r="85" ht="27.75" customHeight="1" spans="1:6">
-      <c r="A85" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="16"/>
-      <c r="F85" s="17"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="24">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A83:D83"/>
     <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A85:D85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="A4:A44"/>
-    <mergeCell ref="A46:A63"/>
-    <mergeCell ref="A65:A83"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="A4:A43"/>
+    <mergeCell ref="A45:A62"/>
+    <mergeCell ref="A64:A82"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="B7:B14"/>
-    <mergeCell ref="B15:B22"/>
-    <mergeCell ref="B23:B33"/>
-    <mergeCell ref="B34:B37"/>
-    <mergeCell ref="B38:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="B54:B63"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="B73:B76"/>
-    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="B15:B21"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B45:B52"/>
+    <mergeCell ref="B53:B62"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="B78:B82"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
